--- a/forms/trg/Formulir_TRG_mvrg.xlsx
+++ b/forms/trg/Formulir_TRG_mvrg.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -686,126 +686,114 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Keahlian anggota banyak yang kosong. Mohon pilih keahlian utama untuk setiap anggota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
           <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>SINTA ID</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>6012345</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ORCID</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Kemajuan pengisian (otomatis)</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Kemajuan pengisian (otomatis)</t>
-        </is>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Anggota tercantum</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>COUNTA(Anggota!B5:B28)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Anggota tercantum</t>
+          <t>Anggota dengan keahlian terpilih</t>
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B27)</f>
+        <f>COUNTA(Anggota!F5:F28)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
-        </is>
-      </c>
-      <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B27" s="8">
-        <f>IF(B25=0,0,B26/B25)</f>
+      <c r="B26" s="8">
+        <f>IF(B24=0,0,B25/B24)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>drh. Zulfikri Mustakdir, M.Si</t>
+          <t>Yenni Yusuf, MD, M.Infect.Dis,PhD</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Parasitology</t>
+          <t>Parasitology, Immunology, Vaccinology, Infectious Diseases</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -962,12 +946,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Abdul Rahim, S.Si., M.Si., Ph.D., Apt.</t>
+          <t>drh. Zulfikri Mustakdir, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +961,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Pharmacology, Pharmacognosy</t>
+          <t>Veterinary Parasitology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -999,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>drh. Zulfikri Mustakdir, M.Si</t>
+          <t>Abdul Rahim, S.Si., M.Si., Ph.D., Apt.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Parasitology</t>
+          <t>Pharmacology, Pharmacognosy</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1036,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Abdul Rahim, S.Si., M.Si., Ph.D., Apt.</t>
+          <t>drh. Zulfikri Mustakdir, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1051,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Pharmacology, Pharmacognosy</t>
+          <t>Veterinary Parasitology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1073,20 +1057,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Professor Shigeto Yoshida</t>
+          <t>Abdul Rahim, S.Si., M.Si., Ph.D., Apt.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Kanazawa University</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n"/>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacology, Pharmacognosy</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1106,12 +1094,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ammar Abdurrahman Hasyim, MD, PhD</t>
+          <t>Professor Shigeto Yoshida</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1139,17 +1127,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Arwansyah, S.Pd, M.Si, PhD</t>
+          <t>Ammar Abdurrahman Hasyim, MD, PhD</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Tadulako University</t>
+          <t>Kanazawa University</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1172,17 +1160,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Hartono, S.Si, S.Pd, M.Biotech, PhD</t>
+          <t>Arwansyah, S.Pd, M.Si, PhD</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Makassar State University</t>
+          <t>Tadulako University</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1205,15 +1193,19 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Mesakh Diki Saputra, S.Si</t>
+          <t>Hartono, S.Si, S.Pd, M.Biotech, PhD</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Makassar State University</t>
+        </is>
+      </c>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
@@ -1234,12 +1226,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Lani Suryani</t>
+          <t>Mesakh Diki Saputra, S.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1263,12 +1255,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nida Hanifah</t>
+          <t>Lani Suryani</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1290,10 +1282,22 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Nida Hanifah</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Our research group mainly focused on malaria vaccine development. However, we also do some studies on malaria drug development and COVID-19 vaccine-related serological studies</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1301,7 +1305,11 @@
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1490,15 +1498,32 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="12" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
